--- a/Xbox-Game-Pass-Dashboard.xlsx
+++ b/Xbox-Game-Pass-Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eca52d2729438a6e/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{FF4374F7-DEBA-46D4-8323-E458C688DE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB166009-B041-4F5B-9D15-54278AC61EA5}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{FF4374F7-DEBA-46D4-8323-E458C688DE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C4987CA-281D-48B5-8248-84676E88266D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="0" firstSheet="3" activeTab="3" xr2:uid="{28DD5B76-0634-4F87-BE60-8BFA7EF2E23B}"/>
   </bookViews>
@@ -1910,31 +1910,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Título 1" xfId="1" builtinId="16"/>
   </cellStyles>
-  <dxfs count="51">
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
+  <dxfs count="43">
     <dxf>
       <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
@@ -2129,11 +2105,11 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Estilo de Segmentação de Dados 1" pivot="0" table="0" count="1" xr9:uid="{9040A31C-C383-4DE3-9A6F-CD19E07D9D31}">
-      <tableStyleElement type="wholeTable" dxfId="50"/>
+      <tableStyleElement type="wholeTable" dxfId="42"/>
     </tableStyle>
     <tableStyle name="SlicerStyleLight6 2" pivot="0" table="0" count="10" xr9:uid="{925B2D29-A97F-4287-B8CB-93212FBCA3F1}">
-      <tableStyleElement type="wholeTable" dxfId="49"/>
-      <tableStyleElement type="headerRow" dxfId="48"/>
+      <tableStyleElement type="wholeTable" dxfId="41"/>
+      <tableStyleElement type="headerRow" dxfId="40"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2461,7 +2437,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Xbox-Game-Pass-Subscription-Analysis.xlsx.xlsx]C̳álculos!Tbl_annual_total</c:name>
+    <c:name>[Xbox-Game-Pass-Dashboard.xlsx]C̳álculos!Tbl_annual_total</c:name>
     <c:fmtId val="12"/>
   </c:pivotSource>
   <c:chart>
@@ -4017,7 +3993,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Xbox-Game-Pass-Subscription-Analysis.xlsx.xlsx]C̳álculos!Tabela dinâmica1</c:name>
+    <c:name>[Xbox-Game-Pass-Dashboard.xlsx]C̳álculos!Tabela dinâmica1</c:name>
     <c:fmtId val="12"/>
   </c:pivotSource>
   <c:chart>
@@ -7424,10 +7400,14 @@
           <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr algn="ctr"/>
+            <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:r>
               <a:rPr lang="pt-BR" sz="1300" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
                 <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:rPr>
               <a:t>REVENUE BY AUTO RENEWAL</a:t>
@@ -7912,7 +7892,7 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>23904</xdr:colOff>
+      <xdr:colOff>2482</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>236</xdr:rowOff>
     </xdr:from>
@@ -7935,8 +7915,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2276774" y="4020062"/>
-          <a:ext cx="10142385" cy="1203504"/>
+          <a:off x="2251251" y="3951715"/>
+          <a:ext cx="10200858" cy="1179115"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -7987,115 +7967,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>23902</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>150485</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>611746</xdr:colOff>
+      <xdr:colOff>391082</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>173293</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="204" name="Retângulo: Cantos Superiores Arredondados 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000CC000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2266972" y="3896091"/>
-          <a:ext cx="10204070" cy="387710"/>
-        </a:xfrm>
-        <a:prstGeom prst="round2SameRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="16823E"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="pt-BR" sz="1300" b="1">
-              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>                             AVERAGE TICKET                                                                                           TOP PLAN</a:t>
-          </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1300" b="1">
-            <a:effectLst/>
-            <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-BR" sz="1300" b="1">
-            <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>545690</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>118753</xdr:rowOff>
+      <xdr:rowOff>118754</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>561587</xdr:colOff>
+      <xdr:colOff>406979</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>85091</xdr:rowOff>
+      <xdr:rowOff>85092</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="C̳álculos!$J$14">
       <xdr:nvSpPr>
@@ -8110,7 +7990,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2798560" y="4326318"/>
+          <a:off x="2643952" y="4315276"/>
           <a:ext cx="3052853" cy="905033"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -8145,7 +8025,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{7E280CE6-6918-4C66-A1C0-1806CB85D205}" type="TxLink">
-            <a:rPr lang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2800" b="0" i="0" u="none" strike="noStrike">
               <a:ln>
                 <a:solidFill>
                   <a:srgbClr val="16823E"/>
@@ -8160,7 +8040,7 @@
             <a:pPr algn="ctr"/>
             <a:t>R$ 24,70</a:t>
           </a:fld>
-          <a:endParaRPr lang="pt-BR" sz="3200">
+          <a:endParaRPr lang="pt-BR" sz="2800">
             <a:ln>
               <a:solidFill>
                 <a:srgbClr val="16823E"/>
@@ -8179,16 +8059,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>496958</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>596349</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>96636</xdr:rowOff>
+      <xdr:rowOff>85592</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>324189</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>276086</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>151927</xdr:rowOff>
+      <xdr:rowOff>140883</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="C̳álculos!$J$15">
       <xdr:nvSpPr>
@@ -8203,8 +8083,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7001567" y="4293158"/>
-          <a:ext cx="5139144" cy="993986"/>
+          <a:off x="5886175" y="4282114"/>
+          <a:ext cx="7432259" cy="993986"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -8520,6 +8400,123 @@
               <a:schemeClr val="bg1"/>
             </a:solidFill>
             <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>279987</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>176037</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>120698</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Retângulo: Cantos Superiores Arredondados 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9354139C-4364-4B40-9E66-2D527C3B4312}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2245947" y="3932697"/>
+          <a:ext cx="10189893" cy="310421"/>
+        </a:xfrm>
+        <a:prstGeom prst="round2SameRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="16823E"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1300" b="1">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>                    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1300" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1300" b="1">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>      AVERAGE</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1300" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> TICKET                                                                                                  TOP PLAN                          </a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1300" b="1">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            <a:ea typeface="+mn-ea"/>
             <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
         </a:p>
@@ -13912,6 +13909,823 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D01F5D06-7185-4D34-AD50-7C14E294C9EA}" name="tbl_PlayaSeasonPass_total" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="B31:C35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="281">
+        <item x="87"/>
+        <item x="61"/>
+        <item x="206"/>
+        <item x="275"/>
+        <item x="112"/>
+        <item x="228"/>
+        <item x="35"/>
+        <item x="253"/>
+        <item x="136"/>
+        <item x="3"/>
+        <item x="161"/>
+        <item x="185"/>
+        <item x="7"/>
+        <item x="88"/>
+        <item x="16"/>
+        <item x="186"/>
+        <item x="162"/>
+        <item x="276"/>
+        <item x="36"/>
+        <item x="254"/>
+        <item x="207"/>
+        <item x="137"/>
+        <item x="62"/>
+        <item x="9"/>
+        <item x="113"/>
+        <item x="229"/>
+        <item x="163"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="63"/>
+        <item x="37"/>
+        <item x="230"/>
+        <item x="255"/>
+        <item x="277"/>
+        <item x="138"/>
+        <item x="89"/>
+        <item x="114"/>
+        <item x="17"/>
+        <item x="187"/>
+        <item x="90"/>
+        <item x="139"/>
+        <item x="18"/>
+        <item x="38"/>
+        <item x="64"/>
+        <item x="231"/>
+        <item x="208"/>
+        <item x="256"/>
+        <item x="278"/>
+        <item x="13"/>
+        <item x="115"/>
+        <item x="164"/>
+        <item x="91"/>
+        <item x="188"/>
+        <item x="19"/>
+        <item x="209"/>
+        <item x="116"/>
+        <item x="257"/>
+        <item x="279"/>
+        <item x="140"/>
+        <item x="65"/>
+        <item x="39"/>
+        <item x="92"/>
+        <item x="210"/>
+        <item x="141"/>
+        <item x="232"/>
+        <item x="258"/>
+        <item x="40"/>
+        <item x="66"/>
+        <item x="117"/>
+        <item x="5"/>
+        <item x="165"/>
+        <item x="14"/>
+        <item x="67"/>
+        <item x="211"/>
+        <item x="189"/>
+        <item x="259"/>
+        <item x="20"/>
+        <item x="93"/>
+        <item x="233"/>
+        <item x="41"/>
+        <item x="142"/>
+        <item x="166"/>
+        <item x="143"/>
+        <item x="94"/>
+        <item x="212"/>
+        <item x="167"/>
+        <item x="68"/>
+        <item x="42"/>
+        <item x="234"/>
+        <item x="118"/>
+        <item x="21"/>
+        <item x="260"/>
+        <item x="144"/>
+        <item x="190"/>
+        <item x="213"/>
+        <item x="168"/>
+        <item x="43"/>
+        <item x="235"/>
+        <item x="119"/>
+        <item x="95"/>
+        <item x="22"/>
+        <item x="69"/>
+        <item x="145"/>
+        <item x="191"/>
+        <item x="169"/>
+        <item x="120"/>
+        <item x="261"/>
+        <item x="96"/>
+        <item x="236"/>
+        <item x="0"/>
+        <item x="23"/>
+        <item x="44"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="97"/>
+        <item x="170"/>
+        <item x="262"/>
+        <item x="237"/>
+        <item x="146"/>
+        <item x="45"/>
+        <item x="24"/>
+        <item x="121"/>
+        <item x="12"/>
+        <item x="2"/>
+        <item x="192"/>
+        <item x="72"/>
+        <item x="263"/>
+        <item x="171"/>
+        <item x="238"/>
+        <item x="46"/>
+        <item x="98"/>
+        <item x="214"/>
+        <item x="147"/>
+        <item x="193"/>
+        <item x="264"/>
+        <item x="99"/>
+        <item x="172"/>
+        <item x="47"/>
+        <item x="122"/>
+        <item x="11"/>
+        <item x="239"/>
+        <item x="148"/>
+        <item x="215"/>
+        <item x="1"/>
+        <item x="25"/>
+        <item x="73"/>
+        <item x="123"/>
+        <item x="216"/>
+        <item x="265"/>
+        <item x="149"/>
+        <item x="240"/>
+        <item x="194"/>
+        <item x="26"/>
+        <item x="48"/>
+        <item x="173"/>
+        <item x="100"/>
+        <item x="74"/>
+        <item x="195"/>
+        <item x="174"/>
+        <item x="124"/>
+        <item x="241"/>
+        <item x="266"/>
+        <item x="49"/>
+        <item x="101"/>
+        <item x="150"/>
+        <item x="217"/>
+        <item x="75"/>
+        <item x="27"/>
+        <item x="151"/>
+        <item x="102"/>
+        <item x="218"/>
+        <item x="242"/>
+        <item x="267"/>
+        <item x="125"/>
+        <item x="50"/>
+        <item x="28"/>
+        <item x="76"/>
+        <item x="196"/>
+        <item x="175"/>
+        <item x="4"/>
+        <item x="126"/>
+        <item x="219"/>
+        <item x="268"/>
+        <item x="77"/>
+        <item x="51"/>
+        <item x="152"/>
+        <item x="243"/>
+        <item x="127"/>
+        <item x="103"/>
+        <item x="244"/>
+        <item x="29"/>
+        <item x="197"/>
+        <item x="176"/>
+        <item x="78"/>
+        <item x="269"/>
+        <item x="52"/>
+        <item x="153"/>
+        <item x="10"/>
+        <item x="79"/>
+        <item x="104"/>
+        <item x="30"/>
+        <item x="177"/>
+        <item x="220"/>
+        <item x="245"/>
+        <item x="270"/>
+        <item x="128"/>
+        <item x="8"/>
+        <item x="154"/>
+        <item x="198"/>
+        <item x="53"/>
+        <item x="31"/>
+        <item x="271"/>
+        <item x="246"/>
+        <item x="105"/>
+        <item x="178"/>
+        <item x="221"/>
+        <item x="80"/>
+        <item x="129"/>
+        <item x="155"/>
+        <item x="54"/>
+        <item x="199"/>
+        <item x="247"/>
+        <item x="55"/>
+        <item x="106"/>
+        <item x="179"/>
+        <item x="81"/>
+        <item x="156"/>
+        <item x="222"/>
+        <item x="200"/>
+        <item x="130"/>
+        <item x="248"/>
+        <item x="56"/>
+        <item x="223"/>
+        <item x="157"/>
+        <item x="131"/>
+        <item x="180"/>
+        <item x="201"/>
+        <item x="82"/>
+        <item x="107"/>
+        <item x="32"/>
+        <item x="158"/>
+        <item x="132"/>
+        <item x="202"/>
+        <item x="83"/>
+        <item x="181"/>
+        <item x="224"/>
+        <item x="249"/>
+        <item x="57"/>
+        <item x="108"/>
+        <item x="203"/>
+        <item x="133"/>
+        <item x="225"/>
+        <item x="109"/>
+        <item x="272"/>
+        <item x="182"/>
+        <item x="84"/>
+        <item x="250"/>
+        <item x="58"/>
+        <item x="110"/>
+        <item x="59"/>
+        <item x="183"/>
+        <item x="226"/>
+        <item x="85"/>
+        <item x="273"/>
+        <item x="159"/>
+        <item x="33"/>
+        <item x="204"/>
+        <item x="251"/>
+        <item x="134"/>
+        <item x="205"/>
+        <item x="60"/>
+        <item x="184"/>
+        <item x="160"/>
+        <item x="274"/>
+        <item x="227"/>
+        <item x="135"/>
+        <item x="86"/>
+        <item x="34"/>
+        <item x="252"/>
+        <item x="111"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de EA Play Season Pass Price" fld="8" baseField="2" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E384577-643E-474E-ABA9-22F3AD6A698D}" name="Tbl_annual_total" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+  <location ref="B20:C23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="281">
+        <item x="87"/>
+        <item x="61"/>
+        <item x="206"/>
+        <item x="275"/>
+        <item x="112"/>
+        <item x="228"/>
+        <item x="35"/>
+        <item x="253"/>
+        <item x="136"/>
+        <item x="3"/>
+        <item x="161"/>
+        <item x="185"/>
+        <item x="7"/>
+        <item x="88"/>
+        <item x="16"/>
+        <item x="186"/>
+        <item x="162"/>
+        <item x="276"/>
+        <item x="36"/>
+        <item x="254"/>
+        <item x="207"/>
+        <item x="137"/>
+        <item x="62"/>
+        <item x="9"/>
+        <item x="113"/>
+        <item x="229"/>
+        <item x="163"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="63"/>
+        <item x="37"/>
+        <item x="230"/>
+        <item x="255"/>
+        <item x="277"/>
+        <item x="138"/>
+        <item x="89"/>
+        <item x="114"/>
+        <item x="17"/>
+        <item x="187"/>
+        <item x="90"/>
+        <item x="139"/>
+        <item x="18"/>
+        <item x="38"/>
+        <item x="64"/>
+        <item x="231"/>
+        <item x="208"/>
+        <item x="256"/>
+        <item x="278"/>
+        <item x="13"/>
+        <item x="115"/>
+        <item x="164"/>
+        <item x="91"/>
+        <item x="188"/>
+        <item x="19"/>
+        <item x="209"/>
+        <item x="116"/>
+        <item x="257"/>
+        <item x="279"/>
+        <item x="140"/>
+        <item x="65"/>
+        <item x="39"/>
+        <item x="92"/>
+        <item x="210"/>
+        <item x="141"/>
+        <item x="232"/>
+        <item x="258"/>
+        <item x="40"/>
+        <item x="66"/>
+        <item x="117"/>
+        <item x="5"/>
+        <item x="165"/>
+        <item x="14"/>
+        <item x="67"/>
+        <item x="211"/>
+        <item x="189"/>
+        <item x="259"/>
+        <item x="20"/>
+        <item x="93"/>
+        <item x="233"/>
+        <item x="41"/>
+        <item x="142"/>
+        <item x="166"/>
+        <item x="143"/>
+        <item x="94"/>
+        <item x="212"/>
+        <item x="167"/>
+        <item x="68"/>
+        <item x="42"/>
+        <item x="234"/>
+        <item x="118"/>
+        <item x="21"/>
+        <item x="260"/>
+        <item x="144"/>
+        <item x="190"/>
+        <item x="213"/>
+        <item x="168"/>
+        <item x="43"/>
+        <item x="235"/>
+        <item x="119"/>
+        <item x="95"/>
+        <item x="22"/>
+        <item x="69"/>
+        <item x="145"/>
+        <item x="191"/>
+        <item x="169"/>
+        <item x="120"/>
+        <item x="261"/>
+        <item x="96"/>
+        <item x="236"/>
+        <item x="0"/>
+        <item x="23"/>
+        <item x="44"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="97"/>
+        <item x="170"/>
+        <item x="262"/>
+        <item x="237"/>
+        <item x="146"/>
+        <item x="45"/>
+        <item x="24"/>
+        <item x="121"/>
+        <item x="12"/>
+        <item x="2"/>
+        <item x="192"/>
+        <item x="72"/>
+        <item x="263"/>
+        <item x="171"/>
+        <item x="238"/>
+        <item x="46"/>
+        <item x="98"/>
+        <item x="214"/>
+        <item x="147"/>
+        <item x="193"/>
+        <item x="264"/>
+        <item x="99"/>
+        <item x="172"/>
+        <item x="47"/>
+        <item x="122"/>
+        <item x="11"/>
+        <item x="239"/>
+        <item x="148"/>
+        <item x="215"/>
+        <item x="1"/>
+        <item x="25"/>
+        <item x="73"/>
+        <item x="123"/>
+        <item x="216"/>
+        <item x="265"/>
+        <item x="149"/>
+        <item x="240"/>
+        <item x="194"/>
+        <item x="26"/>
+        <item x="48"/>
+        <item x="173"/>
+        <item x="100"/>
+        <item x="74"/>
+        <item x="195"/>
+        <item x="174"/>
+        <item x="124"/>
+        <item x="241"/>
+        <item x="266"/>
+        <item x="49"/>
+        <item x="101"/>
+        <item x="150"/>
+        <item x="217"/>
+        <item x="75"/>
+        <item x="27"/>
+        <item x="151"/>
+        <item x="102"/>
+        <item x="218"/>
+        <item x="242"/>
+        <item x="267"/>
+        <item x="125"/>
+        <item x="50"/>
+        <item x="28"/>
+        <item x="76"/>
+        <item x="196"/>
+        <item x="175"/>
+        <item x="4"/>
+        <item x="126"/>
+        <item x="219"/>
+        <item x="268"/>
+        <item x="77"/>
+        <item x="51"/>
+        <item x="152"/>
+        <item x="243"/>
+        <item x="127"/>
+        <item x="103"/>
+        <item x="244"/>
+        <item x="29"/>
+        <item x="197"/>
+        <item x="176"/>
+        <item x="78"/>
+        <item x="269"/>
+        <item x="52"/>
+        <item x="153"/>
+        <item x="10"/>
+        <item x="79"/>
+        <item x="104"/>
+        <item x="30"/>
+        <item x="177"/>
+        <item x="220"/>
+        <item x="245"/>
+        <item x="270"/>
+        <item x="128"/>
+        <item x="8"/>
+        <item x="154"/>
+        <item x="198"/>
+        <item x="53"/>
+        <item x="31"/>
+        <item x="271"/>
+        <item x="246"/>
+        <item x="105"/>
+        <item x="178"/>
+        <item x="221"/>
+        <item x="80"/>
+        <item x="129"/>
+        <item x="155"/>
+        <item x="54"/>
+        <item x="199"/>
+        <item x="247"/>
+        <item x="55"/>
+        <item x="106"/>
+        <item x="179"/>
+        <item x="81"/>
+        <item x="156"/>
+        <item x="222"/>
+        <item x="200"/>
+        <item x="130"/>
+        <item x="248"/>
+        <item x="56"/>
+        <item x="223"/>
+        <item x="157"/>
+        <item x="131"/>
+        <item x="180"/>
+        <item x="201"/>
+        <item x="82"/>
+        <item x="107"/>
+        <item x="32"/>
+        <item x="158"/>
+        <item x="132"/>
+        <item x="202"/>
+        <item x="83"/>
+        <item x="181"/>
+        <item x="224"/>
+        <item x="249"/>
+        <item x="57"/>
+        <item x="108"/>
+        <item x="203"/>
+        <item x="133"/>
+        <item x="225"/>
+        <item x="109"/>
+        <item x="272"/>
+        <item x="182"/>
+        <item x="84"/>
+        <item x="250"/>
+        <item x="58"/>
+        <item x="110"/>
+        <item x="59"/>
+        <item x="183"/>
+        <item x="226"/>
+        <item x="85"/>
+        <item x="273"/>
+        <item x="159"/>
+        <item x="33"/>
+        <item x="204"/>
+        <item x="251"/>
+        <item x="134"/>
+        <item x="205"/>
+        <item x="60"/>
+        <item x="184"/>
+        <item x="160"/>
+        <item x="274"/>
+        <item x="227"/>
+        <item x="135"/>
+        <item x="86"/>
+        <item x="34"/>
+        <item x="252"/>
+        <item x="111"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de Total Value" fld="12" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="12" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="13">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE2860ED-DF54-4F54-9875-F6191175C76E}" name="Tabela dinâmica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B11:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de Total Value" fld="12" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D8656658-254E-40CA-8714-95F4A0EB97D5}" name="Tabela dinâmica5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="B43:C47" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="13">
@@ -14273,7 +15087,7 @@
     <dataField name="Soma de Minecraft Season Pass Price" fld="10" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="29">
+    <format dxfId="23">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14289,7 +15103,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1213DA5F-FBAB-44E5-A6D5-E68A0462F3CB}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="B55:C59" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="13">
@@ -14651,7 +15465,7 @@
     <dataField name="Soma de Total Value" fld="12" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="30">
+    <format dxfId="24">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14702,823 +15516,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D01F5D06-7185-4D34-AD50-7C14E294C9EA}" name="tbl_PlayaSeasonPass_total" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="B31:C35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="281">
-        <item x="87"/>
-        <item x="61"/>
-        <item x="206"/>
-        <item x="275"/>
-        <item x="112"/>
-        <item x="228"/>
-        <item x="35"/>
-        <item x="253"/>
-        <item x="136"/>
-        <item x="3"/>
-        <item x="161"/>
-        <item x="185"/>
-        <item x="7"/>
-        <item x="88"/>
-        <item x="16"/>
-        <item x="186"/>
-        <item x="162"/>
-        <item x="276"/>
-        <item x="36"/>
-        <item x="254"/>
-        <item x="207"/>
-        <item x="137"/>
-        <item x="62"/>
-        <item x="9"/>
-        <item x="113"/>
-        <item x="229"/>
-        <item x="163"/>
-        <item x="15"/>
-        <item x="6"/>
-        <item x="63"/>
-        <item x="37"/>
-        <item x="230"/>
-        <item x="255"/>
-        <item x="277"/>
-        <item x="138"/>
-        <item x="89"/>
-        <item x="114"/>
-        <item x="17"/>
-        <item x="187"/>
-        <item x="90"/>
-        <item x="139"/>
-        <item x="18"/>
-        <item x="38"/>
-        <item x="64"/>
-        <item x="231"/>
-        <item x="208"/>
-        <item x="256"/>
-        <item x="278"/>
-        <item x="13"/>
-        <item x="115"/>
-        <item x="164"/>
-        <item x="91"/>
-        <item x="188"/>
-        <item x="19"/>
-        <item x="209"/>
-        <item x="116"/>
-        <item x="257"/>
-        <item x="279"/>
-        <item x="140"/>
-        <item x="65"/>
-        <item x="39"/>
-        <item x="92"/>
-        <item x="210"/>
-        <item x="141"/>
-        <item x="232"/>
-        <item x="258"/>
-        <item x="40"/>
-        <item x="66"/>
-        <item x="117"/>
-        <item x="5"/>
-        <item x="165"/>
-        <item x="14"/>
-        <item x="67"/>
-        <item x="211"/>
-        <item x="189"/>
-        <item x="259"/>
-        <item x="20"/>
-        <item x="93"/>
-        <item x="233"/>
-        <item x="41"/>
-        <item x="142"/>
-        <item x="166"/>
-        <item x="143"/>
-        <item x="94"/>
-        <item x="212"/>
-        <item x="167"/>
-        <item x="68"/>
-        <item x="42"/>
-        <item x="234"/>
-        <item x="118"/>
-        <item x="21"/>
-        <item x="260"/>
-        <item x="144"/>
-        <item x="190"/>
-        <item x="213"/>
-        <item x="168"/>
-        <item x="43"/>
-        <item x="235"/>
-        <item x="119"/>
-        <item x="95"/>
-        <item x="22"/>
-        <item x="69"/>
-        <item x="145"/>
-        <item x="191"/>
-        <item x="169"/>
-        <item x="120"/>
-        <item x="261"/>
-        <item x="96"/>
-        <item x="236"/>
-        <item x="0"/>
-        <item x="23"/>
-        <item x="44"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="97"/>
-        <item x="170"/>
-        <item x="262"/>
-        <item x="237"/>
-        <item x="146"/>
-        <item x="45"/>
-        <item x="24"/>
-        <item x="121"/>
-        <item x="12"/>
-        <item x="2"/>
-        <item x="192"/>
-        <item x="72"/>
-        <item x="263"/>
-        <item x="171"/>
-        <item x="238"/>
-        <item x="46"/>
-        <item x="98"/>
-        <item x="214"/>
-        <item x="147"/>
-        <item x="193"/>
-        <item x="264"/>
-        <item x="99"/>
-        <item x="172"/>
-        <item x="47"/>
-        <item x="122"/>
-        <item x="11"/>
-        <item x="239"/>
-        <item x="148"/>
-        <item x="215"/>
-        <item x="1"/>
-        <item x="25"/>
-        <item x="73"/>
-        <item x="123"/>
-        <item x="216"/>
-        <item x="265"/>
-        <item x="149"/>
-        <item x="240"/>
-        <item x="194"/>
-        <item x="26"/>
-        <item x="48"/>
-        <item x="173"/>
-        <item x="100"/>
-        <item x="74"/>
-        <item x="195"/>
-        <item x="174"/>
-        <item x="124"/>
-        <item x="241"/>
-        <item x="266"/>
-        <item x="49"/>
-        <item x="101"/>
-        <item x="150"/>
-        <item x="217"/>
-        <item x="75"/>
-        <item x="27"/>
-        <item x="151"/>
-        <item x="102"/>
-        <item x="218"/>
-        <item x="242"/>
-        <item x="267"/>
-        <item x="125"/>
-        <item x="50"/>
-        <item x="28"/>
-        <item x="76"/>
-        <item x="196"/>
-        <item x="175"/>
-        <item x="4"/>
-        <item x="126"/>
-        <item x="219"/>
-        <item x="268"/>
-        <item x="77"/>
-        <item x="51"/>
-        <item x="152"/>
-        <item x="243"/>
-        <item x="127"/>
-        <item x="103"/>
-        <item x="244"/>
-        <item x="29"/>
-        <item x="197"/>
-        <item x="176"/>
-        <item x="78"/>
-        <item x="269"/>
-        <item x="52"/>
-        <item x="153"/>
-        <item x="10"/>
-        <item x="79"/>
-        <item x="104"/>
-        <item x="30"/>
-        <item x="177"/>
-        <item x="220"/>
-        <item x="245"/>
-        <item x="270"/>
-        <item x="128"/>
-        <item x="8"/>
-        <item x="154"/>
-        <item x="198"/>
-        <item x="53"/>
-        <item x="31"/>
-        <item x="271"/>
-        <item x="246"/>
-        <item x="105"/>
-        <item x="178"/>
-        <item x="221"/>
-        <item x="80"/>
-        <item x="129"/>
-        <item x="155"/>
-        <item x="54"/>
-        <item x="199"/>
-        <item x="247"/>
-        <item x="55"/>
-        <item x="106"/>
-        <item x="179"/>
-        <item x="81"/>
-        <item x="156"/>
-        <item x="222"/>
-        <item x="200"/>
-        <item x="130"/>
-        <item x="248"/>
-        <item x="56"/>
-        <item x="223"/>
-        <item x="157"/>
-        <item x="131"/>
-        <item x="180"/>
-        <item x="201"/>
-        <item x="82"/>
-        <item x="107"/>
-        <item x="32"/>
-        <item x="158"/>
-        <item x="132"/>
-        <item x="202"/>
-        <item x="83"/>
-        <item x="181"/>
-        <item x="224"/>
-        <item x="249"/>
-        <item x="57"/>
-        <item x="108"/>
-        <item x="203"/>
-        <item x="133"/>
-        <item x="225"/>
-        <item x="109"/>
-        <item x="272"/>
-        <item x="182"/>
-        <item x="84"/>
-        <item x="250"/>
-        <item x="58"/>
-        <item x="110"/>
-        <item x="59"/>
-        <item x="183"/>
-        <item x="226"/>
-        <item x="85"/>
-        <item x="273"/>
-        <item x="159"/>
-        <item x="33"/>
-        <item x="204"/>
-        <item x="251"/>
-        <item x="134"/>
-        <item x="205"/>
-        <item x="60"/>
-        <item x="184"/>
-        <item x="160"/>
-        <item x="274"/>
-        <item x="227"/>
-        <item x="135"/>
-        <item x="86"/>
-        <item x="34"/>
-        <item x="252"/>
-        <item x="111"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="44" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Soma de EA Play Season Pass Price" fld="8" baseField="2" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="31">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E384577-643E-474E-ABA9-22F3AD6A698D}" name="Tbl_annual_total" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
-  <location ref="B20:C23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="281">
-        <item x="87"/>
-        <item x="61"/>
-        <item x="206"/>
-        <item x="275"/>
-        <item x="112"/>
-        <item x="228"/>
-        <item x="35"/>
-        <item x="253"/>
-        <item x="136"/>
-        <item x="3"/>
-        <item x="161"/>
-        <item x="185"/>
-        <item x="7"/>
-        <item x="88"/>
-        <item x="16"/>
-        <item x="186"/>
-        <item x="162"/>
-        <item x="276"/>
-        <item x="36"/>
-        <item x="254"/>
-        <item x="207"/>
-        <item x="137"/>
-        <item x="62"/>
-        <item x="9"/>
-        <item x="113"/>
-        <item x="229"/>
-        <item x="163"/>
-        <item x="15"/>
-        <item x="6"/>
-        <item x="63"/>
-        <item x="37"/>
-        <item x="230"/>
-        <item x="255"/>
-        <item x="277"/>
-        <item x="138"/>
-        <item x="89"/>
-        <item x="114"/>
-        <item x="17"/>
-        <item x="187"/>
-        <item x="90"/>
-        <item x="139"/>
-        <item x="18"/>
-        <item x="38"/>
-        <item x="64"/>
-        <item x="231"/>
-        <item x="208"/>
-        <item x="256"/>
-        <item x="278"/>
-        <item x="13"/>
-        <item x="115"/>
-        <item x="164"/>
-        <item x="91"/>
-        <item x="188"/>
-        <item x="19"/>
-        <item x="209"/>
-        <item x="116"/>
-        <item x="257"/>
-        <item x="279"/>
-        <item x="140"/>
-        <item x="65"/>
-        <item x="39"/>
-        <item x="92"/>
-        <item x="210"/>
-        <item x="141"/>
-        <item x="232"/>
-        <item x="258"/>
-        <item x="40"/>
-        <item x="66"/>
-        <item x="117"/>
-        <item x="5"/>
-        <item x="165"/>
-        <item x="14"/>
-        <item x="67"/>
-        <item x="211"/>
-        <item x="189"/>
-        <item x="259"/>
-        <item x="20"/>
-        <item x="93"/>
-        <item x="233"/>
-        <item x="41"/>
-        <item x="142"/>
-        <item x="166"/>
-        <item x="143"/>
-        <item x="94"/>
-        <item x="212"/>
-        <item x="167"/>
-        <item x="68"/>
-        <item x="42"/>
-        <item x="234"/>
-        <item x="118"/>
-        <item x="21"/>
-        <item x="260"/>
-        <item x="144"/>
-        <item x="190"/>
-        <item x="213"/>
-        <item x="168"/>
-        <item x="43"/>
-        <item x="235"/>
-        <item x="119"/>
-        <item x="95"/>
-        <item x="22"/>
-        <item x="69"/>
-        <item x="145"/>
-        <item x="191"/>
-        <item x="169"/>
-        <item x="120"/>
-        <item x="261"/>
-        <item x="96"/>
-        <item x="236"/>
-        <item x="0"/>
-        <item x="23"/>
-        <item x="44"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="97"/>
-        <item x="170"/>
-        <item x="262"/>
-        <item x="237"/>
-        <item x="146"/>
-        <item x="45"/>
-        <item x="24"/>
-        <item x="121"/>
-        <item x="12"/>
-        <item x="2"/>
-        <item x="192"/>
-        <item x="72"/>
-        <item x="263"/>
-        <item x="171"/>
-        <item x="238"/>
-        <item x="46"/>
-        <item x="98"/>
-        <item x="214"/>
-        <item x="147"/>
-        <item x="193"/>
-        <item x="264"/>
-        <item x="99"/>
-        <item x="172"/>
-        <item x="47"/>
-        <item x="122"/>
-        <item x="11"/>
-        <item x="239"/>
-        <item x="148"/>
-        <item x="215"/>
-        <item x="1"/>
-        <item x="25"/>
-        <item x="73"/>
-        <item x="123"/>
-        <item x="216"/>
-        <item x="265"/>
-        <item x="149"/>
-        <item x="240"/>
-        <item x="194"/>
-        <item x="26"/>
-        <item x="48"/>
-        <item x="173"/>
-        <item x="100"/>
-        <item x="74"/>
-        <item x="195"/>
-        <item x="174"/>
-        <item x="124"/>
-        <item x="241"/>
-        <item x="266"/>
-        <item x="49"/>
-        <item x="101"/>
-        <item x="150"/>
-        <item x="217"/>
-        <item x="75"/>
-        <item x="27"/>
-        <item x="151"/>
-        <item x="102"/>
-        <item x="218"/>
-        <item x="242"/>
-        <item x="267"/>
-        <item x="125"/>
-        <item x="50"/>
-        <item x="28"/>
-        <item x="76"/>
-        <item x="196"/>
-        <item x="175"/>
-        <item x="4"/>
-        <item x="126"/>
-        <item x="219"/>
-        <item x="268"/>
-        <item x="77"/>
-        <item x="51"/>
-        <item x="152"/>
-        <item x="243"/>
-        <item x="127"/>
-        <item x="103"/>
-        <item x="244"/>
-        <item x="29"/>
-        <item x="197"/>
-        <item x="176"/>
-        <item x="78"/>
-        <item x="269"/>
-        <item x="52"/>
-        <item x="153"/>
-        <item x="10"/>
-        <item x="79"/>
-        <item x="104"/>
-        <item x="30"/>
-        <item x="177"/>
-        <item x="220"/>
-        <item x="245"/>
-        <item x="270"/>
-        <item x="128"/>
-        <item x="8"/>
-        <item x="154"/>
-        <item x="198"/>
-        <item x="53"/>
-        <item x="31"/>
-        <item x="271"/>
-        <item x="246"/>
-        <item x="105"/>
-        <item x="178"/>
-        <item x="221"/>
-        <item x="80"/>
-        <item x="129"/>
-        <item x="155"/>
-        <item x="54"/>
-        <item x="199"/>
-        <item x="247"/>
-        <item x="55"/>
-        <item x="106"/>
-        <item x="179"/>
-        <item x="81"/>
-        <item x="156"/>
-        <item x="222"/>
-        <item x="200"/>
-        <item x="130"/>
-        <item x="248"/>
-        <item x="56"/>
-        <item x="223"/>
-        <item x="157"/>
-        <item x="131"/>
-        <item x="180"/>
-        <item x="201"/>
-        <item x="82"/>
-        <item x="107"/>
-        <item x="32"/>
-        <item x="158"/>
-        <item x="132"/>
-        <item x="202"/>
-        <item x="83"/>
-        <item x="181"/>
-        <item x="224"/>
-        <item x="249"/>
-        <item x="57"/>
-        <item x="108"/>
-        <item x="203"/>
-        <item x="133"/>
-        <item x="225"/>
-        <item x="109"/>
-        <item x="272"/>
-        <item x="182"/>
-        <item x="84"/>
-        <item x="250"/>
-        <item x="58"/>
-        <item x="110"/>
-        <item x="59"/>
-        <item x="183"/>
-        <item x="226"/>
-        <item x="85"/>
-        <item x="273"/>
-        <item x="159"/>
-        <item x="33"/>
-        <item x="204"/>
-        <item x="251"/>
-        <item x="134"/>
-        <item x="205"/>
-        <item x="60"/>
-        <item x="184"/>
-        <item x="160"/>
-        <item x="274"/>
-        <item x="227"/>
-        <item x="135"/>
-        <item x="86"/>
-        <item x="34"/>
-        <item x="252"/>
-        <item x="111"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField dataField="1" numFmtId="44" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Soma de Total Value" fld="12" baseField="0" baseItem="0" numFmtId="44"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="32">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="3">
-    <chartFormat chart="12" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="13">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="14">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE2860ED-DF54-4F54-9875-F6191175C76E}" name="Tabela dinâmica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B11:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField dataField="1" numFmtId="44" showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Soma de Total Value" fld="12" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Subscription_Type" xr10:uid="{EEDC1C27-DC26-4095-BB4C-757BE50D5640}" sourceName="Subscription Type">
   <pivotTables>
@@ -15553,22 +15550,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34E0E886-4200-4B36-97B3-63DB74FF40A0}" name="Tabela1" displayName="Tabela1" ref="A1:M296" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34E0E886-4200-4B36-97B3-63DB74FF40A0}" name="Tabela1" displayName="Tabela1" ref="A1:M296" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A1:M296" xr:uid="{34E0E886-4200-4B36-97B3-63DB74FF40A0}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C4A90516-688A-46BF-9167-EA16C2A8A652}" name="Subscriber ID" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{53DD39D0-2220-4121-9E9D-4EAA7E151C0F}" name="Name" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{4F5FF271-4C57-4BE0-8F2C-F82C8551625C}" name="Plan" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{8C17EB93-79B9-4E55-B8F7-BEB82F8253E9}" name="Start Date" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{48CEDF9B-1689-482A-A828-5CCE7713264A}" name="Auto Renewal" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{78B82374-9AA7-4E38-AE4F-78CDE6C83720}" name="Subscription Price" dataDxfId="40" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{F2433F68-AF33-49D0-B1FB-19A396074EDE}" name="Subscription Type" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{FD4D9C95-F6E5-4933-9068-A71FF7DF9343}" name="EA Play Season Pass" dataDxfId="38"/>
-    <tableColumn id="13" xr3:uid="{978DD0D2-834E-4CE4-A39B-30976086932F}" name="EA Play Season Pass_x000a_Price" dataDxfId="37" dataCellStyle="Moeda"/>
-    <tableColumn id="9" xr3:uid="{6E29F111-C395-4580-9DAD-3407D9E8B1A4}" name="Minecraft Season Pass" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{EF544EAA-7F25-4FD5-A10E-8E62804DB9E3}" name="Minecraft Season Pass Price" dataDxfId="35" dataCellStyle="Moeda"/>
-    <tableColumn id="11" xr3:uid="{7F6EB64A-1F07-4E48-9F0F-AC7D9DCD26F8}" name="Coupon Value" dataDxfId="34" dataCellStyle="Moeda"/>
-    <tableColumn id="12" xr3:uid="{2B04ABC8-DE6F-426E-ADC0-D8AFC68CA58E}" name="Total Value" dataDxfId="33" dataCellStyle="Moeda"/>
+    <tableColumn id="1" xr3:uid="{C4A90516-688A-46BF-9167-EA16C2A8A652}" name="Subscriber ID" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{53DD39D0-2220-4121-9E9D-4EAA7E151C0F}" name="Name" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{4F5FF271-4C57-4BE0-8F2C-F82C8551625C}" name="Plan" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{8C17EB93-79B9-4E55-B8F7-BEB82F8253E9}" name="Start Date" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{48CEDF9B-1689-482A-A828-5CCE7713264A}" name="Auto Renewal" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{78B82374-9AA7-4E38-AE4F-78CDE6C83720}" name="Subscription Price" dataDxfId="32" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{F2433F68-AF33-49D0-B1FB-19A396074EDE}" name="Subscription Type" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{FD4D9C95-F6E5-4933-9068-A71FF7DF9343}" name="EA Play Season Pass" dataDxfId="30"/>
+    <tableColumn id="13" xr3:uid="{978DD0D2-834E-4CE4-A39B-30976086932F}" name="EA Play Season Pass_x000a_Price" dataDxfId="29" dataCellStyle="Moeda"/>
+    <tableColumn id="9" xr3:uid="{6E29F111-C395-4580-9DAD-3407D9E8B1A4}" name="Minecraft Season Pass" dataDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{EF544EAA-7F25-4FD5-A10E-8E62804DB9E3}" name="Minecraft Season Pass Price" dataDxfId="27" dataCellStyle="Moeda"/>
+    <tableColumn id="11" xr3:uid="{7F6EB64A-1F07-4E48-9F0F-AC7D9DCD26F8}" name="Coupon Value" dataDxfId="26" dataCellStyle="Moeda"/>
+    <tableColumn id="12" xr3:uid="{2B04ABC8-DE6F-426E-ADC0-D8AFC68CA58E}" name="Total Value" dataDxfId="25" dataCellStyle="Moeda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
